--- a/Output/Tables/Table_div10_adjusted_malf.xlsx
+++ b/Output/Tables/Table_div10_adjusted_malf.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/estela_blanco_uc_cl/Documents/Contaminación_Malformaciones Congénitas/LUR_DLNM/Output/Tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/estela_blanco_uc_cl/Documents/Contaminación_Malformaciones Congénitas/Pollution_Malformation_TEM/Output/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_51B1051E26453FBDFCD64D46839E1C50797EE435" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDC9237E-D8C7-3E49-98DD-E112040B0EC8}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_286D261F301DF2CBA494564DA7DC1B50797E0434" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B44FFDC0-5E37-A541-9FE0-AEC2541FAD17}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="1" r:id="rId1"/>
@@ -58,37 +58,37 @@
     <t>Trimester 1</t>
   </si>
   <si>
-    <t>0.93 (0.82, 1.05)</t>
-  </si>
-  <si>
-    <t>0.64 (0.29, 1.39)</t>
-  </si>
-  <si>
-    <t>0.66 (0.33, 1.32)</t>
+    <t>0.94 (0.83, 1.06)</t>
+  </si>
+  <si>
+    <t>0.69 (0.32, 1.52)</t>
+  </si>
+  <si>
+    <t>0.69 (0.34, 1.40)</t>
   </si>
   <si>
     <t>Trimester 2</t>
   </si>
   <si>
-    <t>1.04 (0.91, 1.18)</t>
-  </si>
-  <si>
-    <t>1.41 (0.62, 3.17)</t>
-  </si>
-  <si>
-    <t>1.26 (0.61, 2.63)</t>
+    <t>1.07 (0.94, 1.22)</t>
+  </si>
+  <si>
+    <t>1.51 (0.68, 3.37)</t>
+  </si>
+  <si>
+    <t>1.45 (0.69, 3.04)</t>
   </si>
   <si>
     <t>Trimester 3</t>
   </si>
   <si>
-    <t>1.10 (0.97, 1.24)</t>
-  </si>
-  <si>
-    <t>1.49 (0.70, 3.20)</t>
-  </si>
-  <si>
-    <t>1.62 (0.81, 3.22)</t>
+    <t>1.05 (0.92, 1.18)</t>
+  </si>
+  <si>
+    <t>1.25 (0.58, 2.70)</t>
+  </si>
+  <si>
+    <t>1.28 (0.63, 2.57)</t>
   </si>
   <si>
     <t>Land-use regression (sp)</t>
@@ -103,154 +103,154 @@
     <t>0.61 (0.40, 0.92)</t>
   </si>
   <si>
-    <t>0.95 (0.90, 1.01)</t>
-  </si>
-  <si>
-    <t>0.77 (0.39, 1.52)</t>
-  </si>
-  <si>
-    <t>0.72 (0.48, 1.09)</t>
-  </si>
-  <si>
-    <t>0.98 (0.93, 1.04)</t>
-  </si>
-  <si>
-    <t>1.21 (0.61, 2.42)</t>
-  </si>
-  <si>
-    <t>0.90 (0.60, 1.37)</t>
-  </si>
-  <si>
-    <t>0.98 (0.93, 1.03)</t>
-  </si>
-  <si>
-    <t>1.06 (0.55, 2.05)</t>
-  </si>
-  <si>
-    <t>0.93 (0.63, 1.38)</t>
-  </si>
-  <si>
-    <t>0.97 (0.83, 1.14)</t>
-  </si>
-  <si>
-    <t>0.69 (0.25, 1.90)</t>
-  </si>
-  <si>
-    <t>0.80 (0.34, 1.91)</t>
-  </si>
-  <si>
-    <t>1.43 (0.63, 3.23)</t>
-  </si>
-  <si>
-    <t>1.27 (0.61, 2.65)</t>
-  </si>
-  <si>
-    <t>1.08 (0.92, 1.26)</t>
-  </si>
-  <si>
-    <t>1.16 (0.43, 3.16)</t>
-  </si>
-  <si>
-    <t>1.41 (0.59, 3.37)</t>
-  </si>
-  <si>
-    <t>0.95 (0.89, 1.01)</t>
+    <t>0.96 (0.90, 1.01)</t>
+  </si>
+  <si>
+    <t>0.82 (0.42, 1.61)</t>
+  </si>
+  <si>
+    <t>0.74 (0.49, 1.11)</t>
+  </si>
+  <si>
+    <t>0.99 (0.93, 1.04)</t>
+  </si>
+  <si>
+    <t>1.26 (0.63, 2.51)</t>
+  </si>
+  <si>
+    <t>0.94 (0.62, 1.43)</t>
+  </si>
+  <si>
+    <t>0.96 (0.91, 1.02)</t>
+  </si>
+  <si>
+    <t>0.89 (0.46, 1.74)</t>
+  </si>
+  <si>
+    <t>0.83 (0.55, 1.25)</t>
+  </si>
+  <si>
+    <t>0.93 (0.77, 1.11)</t>
+  </si>
+  <si>
+    <t>0.62 (0.19, 2.05)</t>
+  </si>
+  <si>
+    <t>0.66 (0.23, 1.84)</t>
+  </si>
+  <si>
+    <t>1.06 (0.93, 1.22)</t>
+  </si>
+  <si>
+    <t>1.48 (0.64, 3.42)</t>
+  </si>
+  <si>
+    <t>1.41 (0.65, 3.06)</t>
+  </si>
+  <si>
+    <t>0.99 (0.83, 1.20)</t>
+  </si>
+  <si>
+    <t>0.93 (0.29, 2.96)</t>
+  </si>
+  <si>
+    <t>0.98 (0.35, 2.74)</t>
+  </si>
+  <si>
+    <t>0.94 (0.88, 1.00)</t>
+  </si>
+  <si>
+    <t>0.61 (0.27, 1.36)</t>
+  </si>
+  <si>
+    <t>0.64 (0.40, 1.00)</t>
+  </si>
+  <si>
+    <t>1.03 (0.96, 1.10)</t>
+  </si>
+  <si>
+    <t>1.35 (0.67, 2.71)</t>
+  </si>
+  <si>
+    <t>1.13 (0.72, 1.76)</t>
+  </si>
+  <si>
+    <t>0.94 (0.89, 1.01)</t>
   </si>
   <si>
     <t>0.68 (0.31, 1.50)</t>
   </si>
   <si>
-    <t>0.68 (0.43, 1.07)</t>
-  </si>
-  <si>
-    <t>1.02 (0.95, 1.09)</t>
-  </si>
-  <si>
-    <t>1.35 (0.64, 2.83)</t>
-  </si>
-  <si>
-    <t>1.07 (0.67, 1.71)</t>
-  </si>
-  <si>
-    <t>0.97 (0.91, 1.03)</t>
-  </si>
-  <si>
-    <t>0.85 (0.39, 1.85)</t>
-  </si>
-  <si>
-    <t>0.83 (0.54, 1.30)</t>
-  </si>
-  <si>
-    <t>0.92 (0.75, 1.14)</t>
-  </si>
-  <si>
-    <t>0.46 (0.11, 1.92)</t>
-  </si>
-  <si>
-    <t>0.50 (0.15, 1.70)</t>
-  </si>
-  <si>
-    <t>0.95 (0.81, 1.12)</t>
-  </si>
-  <si>
-    <t>0.55 (0.18, 1.64)</t>
-  </si>
-  <si>
-    <t>0.65 (0.26, 1.67)</t>
-  </si>
-  <si>
-    <t>0.98 (0.81, 1.20)</t>
-  </si>
-  <si>
-    <t>0.86 (0.25, 2.98)</t>
-  </si>
-  <si>
-    <t>0.80 (0.27, 2.39)</t>
-  </si>
-  <si>
-    <t>1.03 (0.84, 1.26)</t>
-  </si>
-  <si>
-    <t>0.73 (0.20, 2.74)</t>
-  </si>
-  <si>
-    <t>0.94 (0.30, 2.92)</t>
-  </si>
-  <si>
-    <t>0.94 (0.88, 1.01)</t>
-  </si>
-  <si>
-    <t>0.68 (0.30, 1.51)</t>
-  </si>
-  <si>
-    <t>0.61 (0.38, 0.98)</t>
-  </si>
-  <si>
-    <t>0.98 (0.91, 1.06)</t>
-  </si>
-  <si>
-    <t>0.76 (0.33, 1.73)</t>
-  </si>
-  <si>
-    <t>0.85 (0.52, 1.41)</t>
-  </si>
-  <si>
-    <t>0.99 (0.91, 1.07)</t>
-  </si>
-  <si>
-    <t>1.09 (0.46, 2.58)</t>
-  </si>
-  <si>
-    <t>0.85 (0.51, 1.44)</t>
-  </si>
-  <si>
-    <t>0.99 (0.93, 1.06)</t>
-  </si>
-  <si>
-    <t>0.84 (0.39, 1.84)</t>
-  </si>
-  <si>
-    <t>0.91 (0.58, 1.44)</t>
+    <t>0.71 (0.45, 1.11)</t>
+  </si>
+  <si>
+    <t>0.89 (0.72, 1.10)</t>
+  </si>
+  <si>
+    <t>0.41 (0.10, 1.74)</t>
+  </si>
+  <si>
+    <t>0.42 (0.12, 1.43)</t>
+  </si>
+  <si>
+    <t>0.90 (0.74, 1.08)</t>
+  </si>
+  <si>
+    <t>0.45 (0.12, 1.65)</t>
+  </si>
+  <si>
+    <t>0.48 (0.16, 1.47)</t>
+  </si>
+  <si>
+    <t>0.96 (0.76, 1.21)</t>
+  </si>
+  <si>
+    <t>0.67 (0.14, 3.10)</t>
+  </si>
+  <si>
+    <t>0.65 (0.17, 2.47)</t>
+  </si>
+  <si>
+    <t>0.96 (0.79, 1.16)</t>
+  </si>
+  <si>
+    <t>0.65 (0.18, 2.38)</t>
+  </si>
+  <si>
+    <t>0.70 (0.22, 2.17)</t>
+  </si>
+  <si>
+    <t>0.96 (0.89, 1.04)</t>
+  </si>
+  <si>
+    <t>0.72 (0.30, 1.74)</t>
+  </si>
+  <si>
+    <t>0.65 (0.38, 1.10)</t>
+  </si>
+  <si>
+    <t>0.68 (0.29, 1.61)</t>
+  </si>
+  <si>
+    <t>0.79 (0.47, 1.35)</t>
+  </si>
+  <si>
+    <t>1.01 (0.93, 1.09)</t>
+  </si>
+  <si>
+    <t>1.11 (0.46, 2.67)</t>
+  </si>
+  <si>
+    <t>0.90 (0.53, 1.52)</t>
+  </si>
+  <si>
+    <t>0.97 (0.90, 1.05)</t>
+  </si>
+  <si>
+    <t>0.75 (0.32, 1.73)</t>
+  </si>
+  <si>
+    <t>0.87 (0.52, 1.46)</t>
   </si>
   <si>
     <t>Sheet</t>
@@ -837,13 +837,13 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -854,13 +854,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -871,13 +871,13 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -888,13 +888,13 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -905,13 +905,13 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -924,8 +924,6 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -954,13 +952,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -971,13 +969,13 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -988,13 +986,13 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1005,13 +1003,13 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1022,13 +1020,13 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1039,7 +1037,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
         <v>68</v>

--- a/Output/Tables/Table_div10_adjusted_malf.xlsx
+++ b/Output/Tables/Table_div10_adjusted_malf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/estela_blanco_uc_cl/Documents/Contaminación_Malformaciones Congénitas/Pollution_Malformation_TEM/Output/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_286D261F301DF2CBA494564DA7DC1B50797E0434" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B44FFDC0-5E37-A541-9FE0-AEC2541FAD17}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_286D261F301DF2CBA494564DA7DC1B50797E0434" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3788AA5-7630-D24C-9EC9-6032D50BD26E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="1" r:id="rId1"/>
@@ -924,6 +924,8 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
